--- a/DataXlCalcNet/DataExamples/MainExamples/Workbooks/LoDemoAPY.xlsx
+++ b/DataXlCalcNet/DataExamples/MainExamples/Workbooks/LoDemoAPY.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="GeneralInfo" sheetId="1" state="visible" r:id="rId3"/>
@@ -485,6 +485,55 @@
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>775080</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>96840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Image 1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="812880" y="1625760"/>
+          <a:ext cx="4839120" cy="4811040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1680,59 +1729,59 @@
         <v>100</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f aca="false">AutoAddIn.MpFunlab.apy0("result =  str(sys.path)")</f>
-        <v>['C:\\Python313\\Lib\\site-packages', 'C:\\Python313\\Lib', 'C:\\Python313\\DLLs', 'C:\\Python313', 'C:\\Program Files\\LibreOffice\\program\\python-core-3.13.15\\lib', 'C:\\Program Files\\LibreOffice\\program\\python-core-3.13.15\\lib\\site-packages', 'C:\\Program Files\\LibreOffice\\program', 'C:\\Program Files\\LibreOffice\\program\\python313.zip', 'C:\\Temp\\Python313\\Lib', 'C:\\Temp\\Python313\\DLLs', 'C:\\Program Files\\LibreOffice\\program\\Lib', 'C:\\Program Files\\LibreOffice\\share\\extensions\\dict-en\\pythonpath']</v>
+        <f aca="false">AutoAddIn.MpFunlab.apy0("result = str(sys.path)")</f>
+        <v>['C:\\Users\\DUHad\\Documents\\DataXlCalcNet', 'C:\\Python313\\Lib\\site-packages', 'C:\\Python313\\Lib', 'C:\\Python313\\DLLs', 'C:\\Python313', 'C:\\Program Files\\LibreOffice\\program\\python-core-3.13.15\\lib', 'C:\\Program Files\\LibreOffice\\program\\python-core-3.13.15\\lib\\site-packages', 'C:\\Program Files\\LibreOffice\\program', 'C:\\Program Files\\LibreOffice\\program\\python313.zip', 'C:\\Program Files\\LibreOffice\\program\\Lib', 'C:\\Program Files\\LibreOffice\\share\\extensions\\dict-en\\pythonpath']</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="str">
         <f aca="false" t="array" ref="A4:A13">AutoAddIn.MpFunlab.apy0("result = sys.path",1,0)</f>
-        <v>C:\Python313\Lib\site-packages</v>
+        <v>C:\Users\DUHad\Documents\DataXlCalcNet</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="str">
-        <v>C:\Python313\Lib</v>
+        <v>C:\Python313\Lib\site-packages</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="str">
-        <v>C:\Python313\DLLs</v>
+        <v>C:\Python313\Lib</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="str">
-        <v>C:\Python313</v>
+        <v>C:\Python313\DLLs</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="str">
-        <v>C:\Program Files\LibreOffice\program\python-core-3.13.15\lib</v>
+        <v>C:\Python313</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="str">
-        <v>C:\Program Files\LibreOffice\program\python-core-3.13.15\lib\site-packages</v>
+        <v>C:\Program Files\LibreOffice\program\python-core-3.13.15\lib</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="str">
-        <v>C:\Program Files\LibreOffice\program</v>
+        <v>C:\Program Files\LibreOffice\program\python-core-3.13.15\lib\site-packages</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="str">
-        <v>C:\Program Files\LibreOffice\program\python313.zip</v>
+        <v>C:\Program Files\LibreOffice\program</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="str">
-        <v>C:\Temp\Python313\Lib</v>
+        <v>C:\Program Files\LibreOffice\program\python313.zip</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="str">
-        <v>C:\Temp\Python313\DLLs</v>
+        <v>C:\Program Files\LibreOffice\program\Lib</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1964,10 +2013,10 @@
       </c>
       <c r="B4" s="1" t="n">
         <f aca="false">AutoAddIn.MpFunlab.apy1("temp  = 0 $n for i in range(int(P1)): $n$t temp += i $n result = 2 * temp", C4)</f>
-        <v>1980</v>
+        <v>20880</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,8 +2026,8 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="str">
-        <f aca="false">AutoAddIn.MpFunlab.apy0("from xlcalcnet import mpm $n  mpm.dps=140 $n result = str(mpm.sqrt(2))")</f>
-        <v>1.4142135623730950488016887242096980785696718753769480731766797379907324784621070388503875343276415727350138462309122970249248360558507372126</v>
+        <f aca="false">AutoAddIn.MpFunlab.apy0("from xlcalcnet import mpm $n  mpm.dps=40 $n result = str(mpm.sqrt(2))")</f>
+        <v>1.41421356237309504880168872420969807857</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2068,5 +2117,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>